--- a/tabelas_utentes/sit_and_reach_2_utentes.xlsx
+++ b/tabelas_utentes/sit_and_reach_2_utentes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="10">
   <si>
     <t>Age</t>
   </si>
@@ -457,7 +457,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -470,7 +470,7 @@
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2201,10 +2201,10 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="7">
+      <c r="A73" s="4">
         <v>66</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="5">
         <v>1.54</v>
       </c>
       <c r="C73" s="6"/>
@@ -2214,14 +2214,206 @@
       <c r="E73" s="4">
         <v>2</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="5">
         <v>4.88</v>
       </c>
       <c r="G73" s="5">
         <v>2.88</v>
       </c>
-      <c r="H73" s="7">
+      <c r="H73" s="4">
         <v>50</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+      <c r="A74" s="4">
+        <v>71</v>
+      </c>
+      <c r="B74" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F74" s="5">
+        <v>-3.18</v>
+      </c>
+      <c r="G74" s="5">
+        <v>2.18</v>
+      </c>
+      <c r="H74" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+      <c r="A75" s="4">
+        <v>71</v>
+      </c>
+      <c r="B75" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F75" s="5">
+        <v>-3.67</v>
+      </c>
+      <c r="G75" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H75" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+      <c r="A76" s="4">
+        <v>71</v>
+      </c>
+      <c r="B76" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F76" s="5">
+        <v>-2.09</v>
+      </c>
+      <c r="G76" s="5">
+        <v>1.09</v>
+      </c>
+      <c r="H76" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+      <c r="A77" s="4">
+        <v>71</v>
+      </c>
+      <c r="B77" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="4">
+        <v>2</v>
+      </c>
+      <c r="F77" s="5">
+        <v>2.12</v>
+      </c>
+      <c r="G77" s="5">
+        <v>0.1200000000000001</v>
+      </c>
+      <c r="H77" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+      <c r="A78" s="4">
+        <v>71</v>
+      </c>
+      <c r="B78" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="4">
+        <v>2</v>
+      </c>
+      <c r="F78" s="5">
+        <v>4.91</v>
+      </c>
+      <c r="G78" s="5">
+        <v>2.91</v>
+      </c>
+      <c r="H78" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+      <c r="A79" s="4">
+        <v>71</v>
+      </c>
+      <c r="B79" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="4">
+        <v>2</v>
+      </c>
+      <c r="F79" s="5">
+        <v>4.59</v>
+      </c>
+      <c r="G79" s="5">
+        <v>2.59</v>
+      </c>
+      <c r="H79" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+      <c r="A80" s="4">
+        <v>71</v>
+      </c>
+      <c r="B80" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+      <c r="F80" s="5">
+        <v>3.75</v>
+      </c>
+      <c r="G80" s="5">
+        <v>2.75</v>
+      </c>
+      <c r="H80" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+      <c r="A81" s="7">
+        <v>71</v>
+      </c>
+      <c r="B81" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="4">
+        <v>1</v>
+      </c>
+      <c r="F81" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="G81" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="H81" s="7">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas_utentes/sit_and_reach_2_utentes.xlsx
+++ b/tabelas_utentes/sit_and_reach_2_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3149,15 +3149,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="A105" t="n">
+        <v>60</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1.6</v>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
@@ -3168,17 +3164,229 @@
       <c r="E105" t="n">
         <v>14</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>12.49</t>
-        </is>
+      <c r="F105" t="n">
+        <v>12.49</v>
       </c>
       <c r="G105" t="n">
         <v>1.51</v>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>62</t>
+      <c r="H105" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>76</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H106" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>76</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H107" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>76</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H108" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>76</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.7400000000000002</v>
+      </c>
+      <c r="H109" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>76</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H110" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>76</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6</v>
+      </c>
+      <c r="F111" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H111" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>76</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="H112" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0.1200000000000001</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>64</t>
         </is>
       </c>
     </row>

--- a/tabelas_utentes/sit_and_reach_2_utentes.xlsx
+++ b/tabelas_utentes/sit_and_reach_2_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3357,15 +3357,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
+      <c r="A113" t="n">
+        <v>76</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1.52</v>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
@@ -3376,17 +3372,229 @@
       <c r="E113" t="n">
         <v>6</v>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
+      <c r="F113" t="n">
+        <v>5.88</v>
       </c>
       <c r="G113" t="n">
         <v>0.1200000000000001</v>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>64</t>
+      <c r="H113" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>73</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-17.89</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.1099999999999994</v>
+      </c>
+      <c r="H114" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>73</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-18.61</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2.609999999999999</v>
+      </c>
+      <c r="H115" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>73</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-21</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>73</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-20.92</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.920000000000002</v>
+      </c>
+      <c r="H117" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>73</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-21.01</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.01000000000000156</v>
+      </c>
+      <c r="H118" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>73</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-22.08</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2.079999999999998</v>
+      </c>
+      <c r="H119" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>73</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-20.11</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1.109999999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-19.89</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0.8900000000000006</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>68</t>
         </is>
       </c>
     </row>

--- a/tabelas_utentes/sit_and_reach_2_utentes.xlsx
+++ b/tabelas_utentes/sit_and_reach_2_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3565,15 +3565,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
+      <c r="A121" t="n">
+        <v>73</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1.66</v>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
@@ -3584,17 +3580,229 @@
       <c r="E121" t="n">
         <v>-19</v>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-19.89</t>
-        </is>
+      <c r="F121" t="n">
+        <v>-19.89</v>
       </c>
       <c r="G121" t="n">
         <v>0.8900000000000006</v>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>68</t>
+      <c r="H121" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>82</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-15.71</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.7100000000000009</v>
+      </c>
+      <c r="H122" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>82</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-14.03</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2.029999999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>82</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-10.95</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.050000000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>82</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-13.91</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="H125" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>82</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-17.62</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.620000000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>82</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-17.07</v>
+      </c>
+      <c r="G127" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="H127" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>82</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-10.97</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.9700000000000006</v>
+      </c>
+      <c r="H128" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-10.88</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0.8800000000000008</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>81</t>
         </is>
       </c>
     </row>

--- a/tabelas_utentes/sit_and_reach_2_utentes.xlsx
+++ b/tabelas_utentes/sit_and_reach_2_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3773,15 +3773,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
+      <c r="A129" t="n">
+        <v>82</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1.69</v>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
@@ -3792,17 +3788,437 @@
       <c r="E129" t="n">
         <v>-10</v>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-10.88</t>
-        </is>
+      <c r="F129" t="n">
+        <v>-10.88</v>
       </c>
       <c r="G129" t="n">
         <v>0.8800000000000008</v>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>81</t>
+      <c r="H129" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>75</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>3</v>
+      </c>
+      <c r="F130" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="G130" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H130" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>75</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H131" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>75</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H132" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>75</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H133" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>75</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H134" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>75</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.6200000000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>75</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F136" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.9900000000000002</v>
+      </c>
+      <c r="H136" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>75</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.8599999999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>62</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>-17</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-18.67</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1.670000000000002</v>
+      </c>
+      <c r="H138" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>62</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-9.83</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.130000000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>62</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-13.37</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.369999999999999</v>
+      </c>
+      <c r="H140" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>62</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-16.81</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.8099999999999987</v>
+      </c>
+      <c r="H141" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>62</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-13.27</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.7300000000000004</v>
+      </c>
+      <c r="H142" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>62</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.7899999999999991</v>
+      </c>
+      <c r="H143" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>62</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-17.47</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2.169999999999998</v>
+      </c>
+      <c r="H144" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-13.33</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0.3300000000000001</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>58</t>
         </is>
       </c>
     </row>

--- a/tabelas_utentes/sit_and_reach_2_utentes.xlsx
+++ b/tabelas_utentes/sit_and_reach_2_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4813,15 +4813,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
+      <c r="A169" t="n">
+        <v>70</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1.56</v>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
@@ -4832,17 +4828,437 @@
       <c r="E169" t="n">
         <v>-11</v>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-11.25</t>
-        </is>
+      <c r="F169" t="n">
+        <v>-11.25</v>
       </c>
       <c r="G169" t="n">
         <v>0.25</v>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>69</t>
+      <c r="H169" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>72</v>
+      </c>
+      <c r="B170" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F170" t="n">
+        <v>-11.58</v>
+      </c>
+      <c r="G170" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H170" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>72</v>
+      </c>
+      <c r="B171" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="F171" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="H171" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>72</v>
+      </c>
+      <c r="B172" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F172" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H172" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>72</v>
+      </c>
+      <c r="B173" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="F173" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.2199999999999998</v>
+      </c>
+      <c r="H173" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>72</v>
+      </c>
+      <c r="B174" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F174" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H174" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>72</v>
+      </c>
+      <c r="B175" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>3</v>
+      </c>
+      <c r="F175" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.2200000000000002</v>
+      </c>
+      <c r="H175" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>72</v>
+      </c>
+      <c r="B176" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>4</v>
+      </c>
+      <c r="F176" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H176" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>72</v>
+      </c>
+      <c r="B177" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>4</v>
+      </c>
+      <c r="F177" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="G177" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H177" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>76</v>
+      </c>
+      <c r="B178" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F178" t="n">
+        <v>-23.46</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2.460000000000001</v>
+      </c>
+      <c r="H178" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>76</v>
+      </c>
+      <c r="B179" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F179" t="n">
+        <v>-18.86</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.8599999999999994</v>
+      </c>
+      <c r="H179" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>76</v>
+      </c>
+      <c r="B180" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F180" t="n">
+        <v>-47.69</v>
+      </c>
+      <c r="G180" t="n">
+        <v>6.689999999999998</v>
+      </c>
+      <c r="H180" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>76</v>
+      </c>
+      <c r="B181" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F181" t="n">
+        <v>-22.27</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.7300000000000004</v>
+      </c>
+      <c r="H181" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>76</v>
+      </c>
+      <c r="B182" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>-22</v>
+      </c>
+      <c r="F182" t="n">
+        <v>-20.65</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1.350000000000001</v>
+      </c>
+      <c r="H182" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>76</v>
+      </c>
+      <c r="B183" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F183" t="n">
+        <v>-21.09</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="H183" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>76</v>
+      </c>
+      <c r="B184" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F184" t="n">
+        <v>-23.44</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.5599999999999987</v>
+      </c>
+      <c r="H184" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-21.44</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>0.4400000000000013</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>72</t>
         </is>
       </c>
     </row>

--- a/tabelas_utentes/sit_and_reach_2_utentes.xlsx
+++ b/tabelas_utentes/sit_and_reach_2_utentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5229,15 +5229,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="A185" t="n">
+        <v>76</v>
+      </c>
+      <c r="B185" t="n">
+        <v>1.8</v>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
@@ -5248,17 +5244,437 @@
       <c r="E185" t="n">
         <v>-21</v>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>-21.44</t>
-        </is>
+      <c r="F185" t="n">
+        <v>-21.44</v>
       </c>
       <c r="G185" t="n">
         <v>0.4400000000000013</v>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>72</t>
+      <c r="H185" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>71</v>
+      </c>
+      <c r="B186" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F186" t="n">
+        <v>-12.24</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.2400000000000002</v>
+      </c>
+      <c r="H186" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>71</v>
+      </c>
+      <c r="B187" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F187" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="H187" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>71</v>
+      </c>
+      <c r="B188" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="F188" t="n">
+        <v>-17.11</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1.609999999999999</v>
+      </c>
+      <c r="H188" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>71</v>
+      </c>
+      <c r="B189" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F189" t="n">
+        <v>-16.98</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H189" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>71</v>
+      </c>
+      <c r="B190" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>-16.33</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1.129999999999999</v>
+      </c>
+      <c r="H190" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>71</v>
+      </c>
+      <c r="B191" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F191" t="n">
+        <v>-14.41</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.4100000000000001</v>
+      </c>
+      <c r="H191" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>71</v>
+      </c>
+      <c r="B192" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F192" t="n">
+        <v>-17.72</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1.719999999999999</v>
+      </c>
+      <c r="H192" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>71</v>
+      </c>
+      <c r="B193" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F193" t="n">
+        <v>-18.97</v>
+      </c>
+      <c r="G193" t="n">
+        <v>5.969999999999999</v>
+      </c>
+      <c r="H193" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>75</v>
+      </c>
+      <c r="B194" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F194" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H194" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>75</v>
+      </c>
+      <c r="B195" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>2</v>
+      </c>
+      <c r="F195" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H195" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>75</v>
+      </c>
+      <c r="B196" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F196" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H196" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>75</v>
+      </c>
+      <c r="B197" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>3</v>
+      </c>
+      <c r="F197" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H197" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>75</v>
+      </c>
+      <c r="B198" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>2</v>
+      </c>
+      <c r="F198" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H198" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>75</v>
+      </c>
+      <c r="B199" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>3</v>
+      </c>
+      <c r="F199" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H199" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>75</v>
+      </c>
+      <c r="B200" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H200" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>68</t>
         </is>
       </c>
     </row>
